--- a/docs/fightp.xlsx
+++ b/docs/fightp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t-way\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kellywan\Saved Games\2ndFight\2ndFight\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267EF29E-00B2-4515-858E-AC9683290582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE9CE65-7E2F-48E4-9060-202D1DF58ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F414806E-BD0B-4628-A6E0-4DD16E4EFCF0}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -776,7 +774,7 @@
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:5" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
         <v>1</v>
@@ -808,7 +806,7 @@
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:5" ht="126" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="189" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -817,7 +815,7 @@
       </c>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:5" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="189" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3" t="s">
         <v>19</v>
@@ -1029,5 +1027,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>